--- a/consol.xlsx
+++ b/consol.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://whitecap-my.sharepoint.com/personal/vidhu_mendiratta_wcap_ca/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB0E7099-BC6B-491F-BB2B-7C7872B40995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{FB0E7099-BC6B-491F-BB2B-7C7872B40995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D69789-48B8-4E2F-A792-13354C3FB438}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E9BE747-0D49-481C-B937-EC81851CFBBA}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>VF_BAK_IN_30</t>
   </si>
   <si>
-    <t>VF_BAK_2.0_100</t>
-  </si>
-  <si>
     <t>99/01-27-008-11W2/0</t>
   </si>
   <si>
@@ -635,9 +632,6 @@
     <t>01/16-26-008-10W2/0</t>
   </si>
   <si>
-    <t>VF_BAK_2.0_125</t>
-  </si>
-  <si>
     <t>77/13-27-008-10W2/0</t>
   </si>
   <si>
@@ -971,9 +965,6 @@
     <t>04/04-30-007-07W2/0</t>
   </si>
   <si>
-    <t>VF_BAK_2.0_75</t>
-  </si>
-  <si>
     <t>04/05-18-007-08W2/0</t>
   </si>
   <si>
@@ -1098,6 +1089,15 @@
   </si>
   <si>
     <t>00/01-11-008-05W2/0</t>
+  </si>
+  <si>
+    <t>VF_BAK_2.0_100 (June 2026)</t>
+  </si>
+  <si>
+    <t>VF_BAK_2.0_125 (June 2026)</t>
+  </si>
+  <si>
+    <t>VF_BAK_2.0_75 (June 2026)</t>
   </si>
 </sst>
 </file>
@@ -1471,6 +1471,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511A2F82-9FEB-4A2A-8CE6-8A46D514E348}">
   <dimension ref="A1:F218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1509,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1517,11 +1522,11 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
@@ -1529,7 +1534,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,19 +1542,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,13 +1562,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1571,19 +1576,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1591,13 +1596,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1605,13 +1610,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1619,13 +1624,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1633,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1641,11 +1646,11 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
@@ -1653,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1661,19 +1666,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1681,11 +1686,11 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
@@ -1693,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1701,19 +1706,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1721,13 +1726,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1735,11 +1740,11 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
@@ -1747,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1755,11 +1760,11 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
@@ -1767,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,11 +1780,11 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
@@ -1787,7 +1792,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,11 +1800,11 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
@@ -1807,7 +1812,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,11 +1820,11 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
@@ -1827,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1835,13 +1840,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1849,13 +1854,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,19 +1868,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,11 +1888,11 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
         <v>45</v>
       </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
@@ -1895,7 +1900,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1903,19 +1908,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
         <v>47</v>
       </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,19 +1928,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" t="s">
-        <v>50</v>
-      </c>
       <c r="D26" t="s">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,11 +1948,11 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
@@ -1955,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1963,11 +1968,11 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
         <v>53</v>
       </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
       <c r="D28" t="s">
         <v>9</v>
       </c>
@@ -1975,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1983,19 +1988,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
         <v>55</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
         <v>56</v>
       </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>57</v>
-      </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2003,19 +2008,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
-        <v>59</v>
-      </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2023,19 +2028,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" t="s">
         <v>60</v>
       </c>
-      <c r="C31" t="s">
-        <v>61</v>
-      </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2043,11 +2048,11 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
         <v>62</v>
       </c>
-      <c r="C32" t="s">
-        <v>63</v>
-      </c>
       <c r="D32" t="s">
         <v>9</v>
       </c>
@@ -2055,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,11 +2068,11 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
         <v>64</v>
       </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
       <c r="D33" t="s">
         <v>9</v>
       </c>
@@ -2075,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,19 +2088,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" t="s">
         <v>66</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
         <v>67</v>
       </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>68</v>
-      </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,11 +2108,11 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
@@ -2115,7 +2120,7 @@
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,11 +2128,11 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" t="s">
         <v>71</v>
       </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
       <c r="D36" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2140,7 @@
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,11 +2148,11 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
@@ -2155,7 +2160,7 @@
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,19 +2168,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
         <v>75</v>
       </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,19 +2188,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
         <v>77</v>
       </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,19 +2208,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
         <v>79</v>
       </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
       <c r="D40" t="s">
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,19 +2228,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
         <v>81</v>
       </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,19 +2248,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,11 +2268,11 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
         <v>85</v>
       </c>
-      <c r="C43" t="s">
-        <v>86</v>
-      </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
@@ -2275,7 +2280,7 @@
         <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,11 +2288,11 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
         <v>87</v>
       </c>
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
       <c r="D44" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2300,7 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,11 +2308,11 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
-        <v>90</v>
-      </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
@@ -2315,7 +2320,7 @@
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,13 +2328,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2337,11 +2342,11 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" t="s">
         <v>92</v>
       </c>
-      <c r="C47" t="s">
-        <v>93</v>
-      </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
@@ -2349,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,11 +2362,11 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
         <v>94</v>
       </c>
-      <c r="C48" t="s">
-        <v>95</v>
-      </c>
       <c r="D48" t="s">
         <v>9</v>
       </c>
@@ -2369,7 +2374,7 @@
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2377,11 +2382,11 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
         <v>96</v>
       </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
@@ -2389,7 +2394,7 @@
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2397,13 +2402,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2411,13 +2416,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2425,19 +2430,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" t="s">
         <v>100</v>
       </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2445,13 +2450,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,7 +2464,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2467,7 +2472,7 @@
         <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,13 +2480,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2489,13 +2494,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,19 +2508,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" t="s">
         <v>105</v>
       </c>
-      <c r="C58" t="s">
-        <v>106</v>
-      </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,11 +2528,11 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" t="s">
         <v>107</v>
       </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
@@ -2535,7 +2540,7 @@
         <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2543,11 +2548,11 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" t="s">
         <v>109</v>
       </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
@@ -2555,7 +2560,7 @@
         <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,19 +2568,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" t="s">
         <v>111</v>
       </c>
-      <c r="C61" t="s">
-        <v>112</v>
-      </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,19 +2588,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" t="s">
         <v>113</v>
       </c>
-      <c r="C62" t="s">
-        <v>114</v>
-      </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,19 +2608,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" t="s">
         <v>115</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
         <v>116</v>
       </c>
-      <c r="D63" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>117</v>
-      </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,11 +2628,11 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" t="s">
         <v>118</v>
       </c>
-      <c r="C64" t="s">
-        <v>119</v>
-      </c>
       <c r="D64" t="s">
         <v>9</v>
       </c>
@@ -2635,7 +2640,7 @@
         <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,19 +2648,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" t="s">
         <v>120</v>
       </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,19 +2668,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" t="s">
         <v>122</v>
       </c>
-      <c r="C66" t="s">
-        <v>123</v>
-      </c>
       <c r="D66" t="s">
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,11 +2688,11 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" t="s">
         <v>124</v>
       </c>
-      <c r="C67" t="s">
-        <v>125</v>
-      </c>
       <c r="D67" t="s">
         <v>9</v>
       </c>
@@ -2695,7 +2700,7 @@
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,11 +2708,11 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" t="s">
         <v>126</v>
       </c>
-      <c r="C68" t="s">
-        <v>127</v>
-      </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
@@ -2715,7 +2720,7 @@
         <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,11 +2728,11 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" t="s">
         <v>128</v>
       </c>
-      <c r="C69" t="s">
-        <v>129</v>
-      </c>
       <c r="D69" t="s">
         <v>9</v>
       </c>
@@ -2735,7 +2740,7 @@
         <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,13 +2748,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2757,19 +2762,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>130</v>
+      </c>
+      <c r="C71" t="s">
         <v>131</v>
       </c>
-      <c r="C71" t="s">
-        <v>132</v>
-      </c>
       <c r="D71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2777,19 +2782,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" t="s">
         <v>133</v>
       </c>
-      <c r="C72" t="s">
-        <v>134</v>
-      </c>
       <c r="D72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F72" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2797,11 +2802,11 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" t="s">
         <v>135</v>
       </c>
-      <c r="C73" t="s">
-        <v>136</v>
-      </c>
       <c r="D73" t="s">
         <v>9</v>
       </c>
@@ -2809,7 +2814,7 @@
         <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2817,13 +2822,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2831,19 +2836,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" t="s">
         <v>138</v>
       </c>
-      <c r="C75" t="s">
-        <v>139</v>
-      </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2851,11 +2856,11 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" t="s">
         <v>140</v>
       </c>
-      <c r="C76" t="s">
-        <v>141</v>
-      </c>
       <c r="D76" t="s">
         <v>9</v>
       </c>
@@ -2863,7 +2868,7 @@
         <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2871,7 +2876,7 @@
         <v>76</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2879,11 +2884,11 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" t="s">
         <v>142</v>
       </c>
-      <c r="C78" t="s">
-        <v>143</v>
-      </c>
       <c r="D78" t="s">
         <v>8</v>
       </c>
@@ -2891,7 +2896,7 @@
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2899,11 +2904,11 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" t="s">
         <v>144</v>
       </c>
-      <c r="C79" t="s">
-        <v>145</v>
-      </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
@@ -2911,7 +2916,7 @@
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2919,19 +2924,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80" t="s">
         <v>146</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" t="s">
         <v>147</v>
       </c>
-      <c r="D80" t="s">
-        <v>24</v>
-      </c>
-      <c r="E80" t="s">
-        <v>148</v>
-      </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2939,13 +2944,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,19 +2958,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>149</v>
+      </c>
+      <c r="C82" t="s">
         <v>150</v>
       </c>
-      <c r="C82" t="s">
-        <v>151</v>
-      </c>
       <c r="D82" t="s">
         <v>8</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,11 +2978,11 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" t="s">
         <v>152</v>
       </c>
-      <c r="C83" t="s">
-        <v>153</v>
-      </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
@@ -2985,7 +2990,7 @@
         <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2993,19 +2998,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" t="s">
         <v>154</v>
       </c>
-      <c r="C84" t="s">
-        <v>155</v>
-      </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3013,13 +3018,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3027,19 +3032,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>156</v>
+      </c>
+      <c r="C86" t="s">
         <v>157</v>
       </c>
-      <c r="C86" t="s">
-        <v>158</v>
-      </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3047,11 +3052,11 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" t="s">
         <v>159</v>
       </c>
-      <c r="C87" t="s">
-        <v>160</v>
-      </c>
       <c r="D87" t="s">
         <v>9</v>
       </c>
@@ -3059,7 +3064,7 @@
         <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3067,11 +3072,11 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>160</v>
+      </c>
+      <c r="C88" t="s">
         <v>161</v>
       </c>
-      <c r="C88" t="s">
-        <v>162</v>
-      </c>
       <c r="D88" t="s">
         <v>9</v>
       </c>
@@ -3079,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3087,11 +3092,11 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>162</v>
+      </c>
+      <c r="C89" t="s">
         <v>163</v>
       </c>
-      <c r="C89" t="s">
-        <v>164</v>
-      </c>
       <c r="D89" t="s">
         <v>9</v>
       </c>
@@ -3099,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3107,11 +3112,11 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" t="s">
         <v>165</v>
       </c>
-      <c r="C90" t="s">
-        <v>166</v>
-      </c>
       <c r="D90" t="s">
         <v>9</v>
       </c>
@@ -3119,7 +3124,7 @@
         <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3127,10 +3132,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
@@ -3139,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3147,11 +3152,11 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" t="s">
         <v>167</v>
       </c>
-      <c r="C92" t="s">
-        <v>168</v>
-      </c>
       <c r="D92" t="s">
         <v>9</v>
       </c>
@@ -3159,7 +3164,7 @@
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3167,19 +3172,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" t="s">
         <v>169</v>
       </c>
-      <c r="C93" t="s">
-        <v>170</v>
-      </c>
       <c r="D93" t="s">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3187,11 +3192,11 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" t="s">
         <v>171</v>
       </c>
-      <c r="C94" t="s">
-        <v>172</v>
-      </c>
       <c r="D94" t="s">
         <v>8</v>
       </c>
@@ -3199,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3207,7 +3212,7 @@
         <v>94</v>
       </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,13 +3220,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3229,11 +3234,11 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" t="s">
         <v>174</v>
       </c>
-      <c r="C97" t="s">
-        <v>175</v>
-      </c>
       <c r="D97" t="s">
         <v>8</v>
       </c>
@@ -3241,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3249,13 +3254,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,13 +3268,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3277,19 +3282,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" t="s">
         <v>178</v>
       </c>
-      <c r="C100" t="s">
-        <v>179</v>
-      </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3297,11 +3302,11 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>179</v>
+      </c>
+      <c r="C101" t="s">
         <v>180</v>
       </c>
-      <c r="C101" t="s">
-        <v>181</v>
-      </c>
       <c r="D101" t="s">
         <v>9</v>
       </c>
@@ -3309,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3317,13 +3322,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3331,19 +3336,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>182</v>
+      </c>
+      <c r="C103" t="s">
         <v>183</v>
       </c>
-      <c r="C103" t="s">
-        <v>184</v>
-      </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3351,11 +3356,11 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>184</v>
+      </c>
+      <c r="C104" t="s">
         <v>185</v>
       </c>
-      <c r="C104" t="s">
-        <v>186</v>
-      </c>
       <c r="D104" t="s">
         <v>9</v>
       </c>
@@ -3363,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3371,7 +3376,7 @@
         <v>104</v>
       </c>
       <c r="F105" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3379,7 +3384,7 @@
         <v>105</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3387,13 +3392,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F107" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,11 +3406,11 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>187</v>
+      </c>
+      <c r="C108" t="s">
         <v>188</v>
       </c>
-      <c r="C108" t="s">
-        <v>189</v>
-      </c>
       <c r="D108" t="s">
         <v>9</v>
       </c>
@@ -3413,7 +3418,7 @@
         <v>9</v>
       </c>
       <c r="F108" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3421,11 +3426,11 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>189</v>
+      </c>
+      <c r="C109" t="s">
         <v>190</v>
       </c>
-      <c r="C109" t="s">
-        <v>191</v>
-      </c>
       <c r="D109" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3438,7 @@
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,11 +3446,11 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>191</v>
+      </c>
+      <c r="C110" t="s">
         <v>192</v>
       </c>
-      <c r="C110" t="s">
-        <v>193</v>
-      </c>
       <c r="D110" t="s">
         <v>9</v>
       </c>
@@ -3453,7 +3458,7 @@
         <v>9</v>
       </c>
       <c r="F110" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,13 +3466,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D111" t="s">
         <v>9</v>
       </c>
       <c r="F111" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,19 +3480,19 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>194</v>
+      </c>
+      <c r="C112" t="s">
         <v>195</v>
       </c>
-      <c r="C112" t="s">
-        <v>196</v>
-      </c>
       <c r="D112" t="s">
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F112" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,13 +3500,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F113" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3509,7 +3514,7 @@
         <v>113</v>
       </c>
       <c r="F114" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3517,19 +3522,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C115" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3537,19 +3542,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C116" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3557,7 +3562,7 @@
         <v>116</v>
       </c>
       <c r="F117" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3565,19 +3570,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C118" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
       </c>
       <c r="F118" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3585,10 +3590,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C119" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -3597,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3605,13 +3610,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F120" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3619,19 +3624,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C121" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D121" t="s">
         <v>8</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F121" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,13 +3644,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F122" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3653,19 +3658,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C123" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D123" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F123" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3673,19 +3678,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C124" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F124" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3693,10 +3698,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C125" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -3705,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="F125" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3713,10 +3718,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C126" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -3725,7 +3730,7 @@
         <v>9</v>
       </c>
       <c r="F126" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3733,19 +3738,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C127" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
       </c>
       <c r="E127" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F127" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3753,19 +3758,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C128" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F128" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3773,19 +3778,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C129" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F129" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3793,7 +3798,7 @@
         <v>129</v>
       </c>
       <c r="F130" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,7 +3806,7 @@
         <v>130</v>
       </c>
       <c r="F131" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,13 +3814,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F132" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3823,10 +3828,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C133" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
@@ -3835,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3843,13 +3848,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,7 +3862,7 @@
         <v>134</v>
       </c>
       <c r="F135" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3865,13 +3870,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
       </c>
       <c r="F136" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3879,19 +3884,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C137" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
       </c>
       <c r="E137" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F137" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3899,19 +3904,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C138" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F138" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -3919,19 +3924,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C139" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F139" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,19 +3944,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C140" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
       </c>
       <c r="F140" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,19 +3964,19 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C141" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F141" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,10 +3984,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C142" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
@@ -3991,7 +3996,7 @@
         <v>8</v>
       </c>
       <c r="F142" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -3999,19 +4004,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C143" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F143" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,7 +4024,7 @@
         <v>143</v>
       </c>
       <c r="F144" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4027,10 +4032,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C145" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
@@ -4039,7 +4044,7 @@
         <v>8</v>
       </c>
       <c r="F145" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4047,19 +4052,19 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C146" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4067,19 +4072,19 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C147" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4087,10 +4092,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C148" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
@@ -4099,7 +4104,7 @@
         <v>8</v>
       </c>
       <c r="F148" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4107,13 +4112,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4121,7 +4126,7 @@
         <v>149</v>
       </c>
       <c r="F150" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,19 +4134,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C151" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F151" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4149,19 +4154,19 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C152" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D152" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
       </c>
       <c r="F152" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4169,10 +4174,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C153" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
@@ -4181,7 +4186,7 @@
         <v>9</v>
       </c>
       <c r="F153" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4189,19 +4194,19 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C154" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F154" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4209,19 +4214,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C155" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
       </c>
       <c r="F155" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4229,10 +4234,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C156" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -4241,7 +4246,7 @@
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4249,13 +4254,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
       </c>
       <c r="F157" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4263,10 +4268,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C158" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
@@ -4275,7 +4280,7 @@
         <v>9</v>
       </c>
       <c r="F158" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4283,13 +4288,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F159" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,19 +4302,19 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F160" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,13 +4322,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D161" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F161" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,10 +4336,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
@@ -4343,7 +4348,7 @@
         <v>9</v>
       </c>
       <c r="F162" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4351,10 +4356,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C163" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>8</v>
@@ -4363,7 +4368,7 @@
         <v>9</v>
       </c>
       <c r="F163" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4371,10 +4376,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C164" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
@@ -4383,7 +4388,7 @@
         <v>8</v>
       </c>
       <c r="F164" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4391,10 +4396,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C165" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -4403,7 +4408,7 @@
         <v>9</v>
       </c>
       <c r="F165" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,7 +4416,7 @@
         <v>165</v>
       </c>
       <c r="F166" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,13 +4424,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
       </c>
       <c r="F167" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,13 +4438,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F168" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4447,13 +4452,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
         <v>9</v>
       </c>
       <c r="F169" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4461,10 +4466,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C170" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D170" t="s">
         <v>8</v>
@@ -4473,7 +4478,7 @@
         <v>8</v>
       </c>
       <c r="F170" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4481,19 +4486,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C171" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F171" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4501,19 +4506,19 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C172" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F172" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4521,19 +4526,19 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C173" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
       </c>
       <c r="F173" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4541,10 +4546,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C174" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -4553,7 +4558,7 @@
         <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4561,7 +4566,7 @@
         <v>174</v>
       </c>
       <c r="F175" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -4569,19 +4574,19 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C176" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D176" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
       </c>
       <c r="F176" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4589,19 +4594,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C177" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D177" t="s">
         <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F177" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -4609,7 +4614,7 @@
         <v>177</v>
       </c>
       <c r="F178" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,13 +4622,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
       </c>
       <c r="F179" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -4631,13 +4636,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F180" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,13 +4650,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D181" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F181" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,10 +4664,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C182" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D182" t="s">
         <v>8</v>
@@ -4671,7 +4676,7 @@
         <v>8</v>
       </c>
       <c r="F182" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4679,19 +4684,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C183" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D183" t="s">
         <v>8</v>
       </c>
       <c r="E183" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F183" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,19 +4704,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C184" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E184" t="s">
         <v>9</v>
       </c>
       <c r="F184" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,10 +4724,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C185" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -4731,7 +4736,7 @@
         <v>9</v>
       </c>
       <c r="F185" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -4739,10 +4744,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C186" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D186" t="s">
         <v>9</v>
@@ -4751,7 +4756,7 @@
         <v>9</v>
       </c>
       <c r="F186" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,10 +4764,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C187" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D187" t="s">
         <v>9</v>
@@ -4771,7 +4776,7 @@
         <v>9</v>
       </c>
       <c r="F187" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -4779,13 +4784,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
       </c>
       <c r="F188" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -4793,19 +4798,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C189" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D189" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F189" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,13 +4818,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D190" t="s">
         <v>9</v>
       </c>
       <c r="F190" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -4827,10 +4832,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C191" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
@@ -4839,7 +4844,7 @@
         <v>9</v>
       </c>
       <c r="F191" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,10 +4852,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C192" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D192" t="s">
         <v>9</v>
@@ -4859,7 +4864,7 @@
         <v>9</v>
       </c>
       <c r="F192" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -4867,13 +4872,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D193" t="s">
         <v>8</v>
       </c>
       <c r="F193" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -4881,19 +4886,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C194" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D194" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E194" t="s">
         <v>9</v>
       </c>
       <c r="F194" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -4901,10 +4906,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C195" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
@@ -4913,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="F195" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -4921,13 +4926,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
       </c>
       <c r="F196" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,19 +4940,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C197" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D197" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
       </c>
       <c r="F197" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,10 +4960,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C198" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D198" t="s">
         <v>9</v>
@@ -4967,7 +4972,7 @@
         <v>9</v>
       </c>
       <c r="F198" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,19 +4980,19 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C199" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D199" t="s">
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F199" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -4995,13 +5000,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
       </c>
       <c r="F200" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5009,19 +5014,19 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F201" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5029,19 +5034,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C202" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E202" t="s">
         <v>9</v>
       </c>
       <c r="F202" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5049,13 +5054,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D203" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F203" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5063,7 +5068,7 @@
         <v>203</v>
       </c>
       <c r="F204" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5071,19 +5076,19 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C205" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D205" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
       </c>
       <c r="F205" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5091,10 +5096,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C206" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
@@ -5103,7 +5108,7 @@
         <v>9</v>
       </c>
       <c r="F206" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5111,19 +5116,19 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C207" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D207" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
       </c>
       <c r="F207" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5131,19 +5136,19 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C208" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D208" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E208" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F208" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -5151,19 +5156,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C209" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D209" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E209" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F209" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5171,7 +5176,7 @@
         <v>209</v>
       </c>
       <c r="F210" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5179,13 +5184,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
       </c>
       <c r="F211" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5193,10 +5198,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C212" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
@@ -5205,7 +5210,7 @@
         <v>9</v>
       </c>
       <c r="F212" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,10 +5218,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C213" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
@@ -5225,7 +5230,7 @@
         <v>9</v>
       </c>
       <c r="F213" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5233,19 +5238,19 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C214" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D214" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E214" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F214" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5253,19 +5258,19 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C215" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D215" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E215" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F215" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -5273,19 +5278,19 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C216" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D216" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E216" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F216" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5293,19 +5298,19 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C217" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D217" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E217" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F217" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,19 +5318,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C218" t="s">
+        <v>349</v>
+      </c>
+      <c r="D218" t="s">
+        <v>67</v>
+      </c>
+      <c r="E218" t="s">
+        <v>23</v>
+      </c>
+      <c r="F218" t="s">
         <v>352</v>
-      </c>
-      <c r="D218" t="s">
-        <v>68</v>
-      </c>
-      <c r="E218" t="s">
-        <v>24</v>
-      </c>
-      <c r="F218" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
